--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:12:38+00:00</t>
+    <t>2026-09-14T19:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -951,7 +951,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="48676-1"/&gt;
-  &lt;display value="HER2 [Interpretation] in Tissue"/&gt;
+  &lt;display value="HER2 Ag [Interpretation] in Tissue"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T19:45:33+00:00</t>
+    <t>2026-09-14T20:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:15:28+00:00</t>
+    <t>2026-09-14T20:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:43:02+00:00</t>
+    <t>2026-09-14T21:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:08:50+00:00</t>
+    <t>2026-09-14T21:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T21:38:27+00:00</t>
+    <t>2026-09-14T22:18:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
+++ b/branches/chore/onko-ballot-repin/StructureDefinition-mii-pr-mtb-biomarker-her2-status.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T22:18:02+00:00</t>
+    <t>2026-09-14T22:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
